--- a/DATA/MACHINE_LEARNING/C13_MACHINE_LEARNING/Diagnostico/Exp04/diagnostico_estadistico_ml.xlsx
+++ b/DATA/MACHINE_LEARNING/C13_MACHINE_LEARNING/Diagnostico/Exp04/diagnostico_estadistico_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,14 +453,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Precipitacion_mm</t>
+          <t>ONI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.657</v>
+        <v>0.891</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -471,83 +471,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ONI</t>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.891</v>
+        <v>-3.296</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Evaluar estandarización.</t>
+          <t>Considerar escalamiento robusto.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Radiacion_Solar</t>
+          <t>Precipitacion_mm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.436</v>
+        <v>0.657</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No requiere transformación.</t>
+          <t>Evaluar estandarización.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Humedad_Relativa</t>
+          <t>Radiacion_Solar</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.056</v>
+        <v>0.436</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Considerar escalamiento robusto.</t>
+          <t>No requiere transformación.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Temp_Min_C</t>
+          <t>irca</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.216</v>
+        <v>1.018</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No requiere transformación.</t>
+          <t>Considerar escalamiento robusto.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -561,50 +561,72 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Velocidad_Viento</t>
+          <t>Humedad_Relativa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.68</v>
+        <v>-1.056</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Evaluar estandarización.</t>
+          <t>Considerar escalamiento robusto.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>irca</t>
+          <t>Temp_Min_C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.854</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>-0.216</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Variable binaria. No requiere transformación.</t>
+          <t>No requiere transformación.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VolumenUtilDiarioMasa</t>
+          <t>Mes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.024</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Variable binaria. No requiere transformación.</t>
+          <t>No requiere transformación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Evaluar estandarización.</t>
         </is>
       </c>
     </row>
